--- a/test_30_each_ground_truth.xlsx
+++ b/test_30_each_ground_truth.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\vantage2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\project1\vantage2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{416009D3-8042-409A-BD3C-859AD8623DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7424E994-A3EC-4D5B-A06B-0A28778A238E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{17CA7A62-8DFB-4760-A10C-7DB6E3DBD05E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="230">
   <si>
     <t>Question</t>
   </si>
@@ -1221,188 +1221,16 @@
     <t>Code not done or completely wrong</t>
   </si>
   <si>
-    <t>#include&lt;simplecpp&gt;
-main_program
-{
-	long double n,r;
-	cin&gt;&gt;n&gt;&gt;r;
-	long double b=n;
-	long double d=n-r;
-	long double a=1;
-	long double c=1;
-	for(int i=1; i&lt;=n-r; i++)
-	{
-		a=a*b;
-		--b;
-		c=c*d;
-		--d;
-	}
-	long double ans=(a/c);
-	cout&lt;&lt;ans;
-}</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
     <t>Quality and number of Comments</t>
   </si>
   <si>
-    <t>#include&lt;iostream&gt;
-using namespace std;
-void sorted_array(int *A, int n){
-                           for(int j=0; j&lt;n; j++){
-                              for(int x=j+1; x&lt;n; x++){
-                                   if(A[j]&gt;A[x]) swap(&amp;A[j] &amp;A[x]);
-                                 }
-                                 }
-                                 } 
-int main() {
-            int N;
-             cin&gt;&gt;N;
-            int A[30];
-             if (N&lt;25){
-               for(int i=0; i&lt;N; i++){
-                                    cin&gt;&gt;A[i];
-                                 }
-                                 }
-                sorted_array(A, N);
-                for(int m=0; m&lt;N; m++){
-                  cout&lt;&lt;" "&lt;&lt;A[m];
-                  }
-                  }</t>
-  </si>
-  <si>
-    <t>Write a C++ program to collect a positive integer n from the user, and then collect n character strings from the user (containing only lower case alphabets and no other characters, not even spaces). The strings need not be of equal length but the maximum length of any string should be 11. The strings should be stored in an appropriate 2D array. Your program should then include the following:
-A function string_compare which takes two strings as input and returns 1 if the first string appears before the second string in alphabetical order, -1 if the second string appears before the first in alphabetical order, and 0 if the two strings are equal to each other. Do not use the inbuilt strcmp function.
-A function string_sort which sorts the character strings using the mergesort algorithm taught in class. You are recommended to write a recursive implementation. You will automatically lose 50% of the marks for this program if you implemented the sorting within main.
-Your program should then print out the strings in sorted alphabetical order, starting from the first to the last. Feel free to refer to the lecture slides for help.
-Input Format
-integer n, and a set of n character strings
-Output Format
-Print out the strings in the suggested order, one string on a new line
-Constraints
-n is a positive integer, n &lt;= 15
-For ease of display of the output, the maximum length of any of the strings should be 11, excluding the NULL character
-The character strings should contain only lower case alphabets
-Sample input and output
-Input
-Output
-4
-zebra
-lion
-tiger
-monkey
-lion
-monkey
-tiger
-zebra
-Note:  
-Do not write any C++ statements for printing general messages. For example, the following should NOT be present in your program: 
-cout &lt;&lt; "Enter a number:",  
-cout &lt;&lt; "The computed answer is", etc.  
-cout should be used to print only the computed final output. In addition, do not print unnecessary spaces unless specified in the program.</t>
-  </si>
-  <si>
-    <t>Reading &amp; storing Input</t>
-  </si>
-  <si>
-    <t>Correctly Stores inputs in an appropriate 2D array accounting for max length of 11 for a string &amp; Reads Inputs</t>
-  </si>
-  <si>
-    <t>Doesn't store input correctly in a 2D array but reading input is correct</t>
-  </si>
-  <si>
-    <t>Fails To Read Input strings correctly</t>
-  </si>
-  <si>
-    <t>#include&lt;iostream&gt;
-#include&lt;cstring&gt;
-using namespace std;
-int main(){
-	int n ;
-	cin&gt;&gt;n;
-	string s1, s2 , s3, s4,s5,s6,s7,s8,s9,s10,s11;
-	getline(cin , s1);
-	getline(cin , s2);
-	getline(cin , s3);
-	getline(cin , s4);
-	getline(cin , s5);
-	getline(cin , s6);
-	getline(cin , s7);
-	getline(cin , s8);
-	getline(cin , s9);
-	getline(cin , s10);
-		getline(cin , s11);
-	for(int i= 97 ;i&lt;124;i++ )
-	{
-		if(s1[0]==char(i)){cout&lt;&lt;s1&lt;&lt;endl;}
-		if(s2[0]==char(i)){cout&lt;&lt;s2&lt;&lt;endl;}
-		if(s3[0]==char(i)){cout&lt;&lt;s3&lt;&lt;endl;}
-		if(s4[0]==char(i)){cout&lt;&lt;s4&lt;&lt;endl;}
-		if(s5[0]==char(i)){cout&lt;&lt;s5&lt;&lt;endl;}
-		if(s6[0]==char(i)){cout&lt;&lt;s6&lt;&lt;endl;}
-		if(s7[0]==char(i)){cout&lt;&lt;s7&lt;&lt;endl;}
-		if(s8[0]==char(i)){cout&lt;&lt;s8&lt;&lt;endl;}
-	    if(s9[0]==char(i)){cout&lt;&lt;s9&lt;&lt;endl;}
-		if(s10[0]==char(i)){cout&lt;&lt;s10&lt;&lt;endl;}
-		if(s11[0]==char(i)){cout&lt;&lt;s11&lt;&lt;endl;}
-	}}</t>
-  </si>
-  <si>
-    <t>Write a program that takes as input two complex numbers and performs one of the following operations on them: addition, subtraction, multiplication, or division. The output should be the result of the operation, with 3 digits after the decimal point. The input should be two pairs of floating-point numbers indicating the real and imaginary parts of the complex numbers, separated by spaces, followed by a letter indicating the operation to be performed. The output should be two space-separated numbers, with the real part followed by the imaginary part.</t>
-  </si>
-  <si>
     <t>Good variable names</t>
   </si>
   <si>
     <t>Poor Variable Names</t>
-  </si>
-  <si>
-    <t>#include &lt;simplecpp&gt;
-main_program {
-     float a,b,p,q;
-     cin &gt;&gt; a &gt;&gt; p &gt;&gt; b &gt;&gt; q;     //  a and b are Real &amp; p and Img
-     cout &lt;&lt;"A"&lt;&lt;endl;
-      cout &lt;&lt; a+b &lt;&lt;" "&lt;&lt; p+q &lt;&lt;" "&lt;&lt;endl;
-      cout &lt;&lt; fixed;
-      cout.precision(3);     
-}</t>
-  </si>
-  <si>
-    <t>You are given a sequence of integers. Your task is to reverse the sequence, print it, and then replace all odd numbers in the original sequence with 0 and print the modified sequence.
-Your Task
-1. Read an integer N representing the number of elements.
-2. Read N integers into an array/vector.
-3. Print the elements in reverse order.
-4. Traverse the original array and replace every odd number with 0.
-5. Print the updated array after replacement.
-Input Format
-- An integer N.
-- N integers representing the elements.
-Output Format
-- First line: Print the array in reverse order with spaces.
-- Second line: Print the modified array where all odd numbers are replaced by 0.
-Assumptions on Input
-- 1 &lt;= N &lt;= 10^5
-- Elements are integers.</t>
-  </si>
-  <si>
-    <t>Declaration of variables and array/vector</t>
-  </si>
-  <si>
-    <t>correctly declares the variable n, and array/vector</t>
-  </si>
-  <si>
-    <t>ay [1];
-{}#include&lt;iostream&gt;
-using namespace std;
-int main{} {
-   int 1;
-   int array a;
-   cin &gt;&gt; a;
-}
-cin &gt;&gt; arr</t>
   </si>
   <si>
     <t>Title - Sorting strings using insertion sort
@@ -1419,86 +1247,13 @@
 Output (on console): zbdf word efs abc 4 2</t>
   </si>
   <si>
-    <t>Sorting algorithm implemented is insertion sort.</t>
-  </si>
-  <si>
     <t>Fully correct</t>
   </si>
   <si>
     <t>Almost correct</t>
   </si>
   <si>
-    <t>Tried in somewhat right direction (e.g., different sorting algorithm)</t>
-  </si>
-  <si>
     <t>totally wrong</t>
-  </si>
-  <si>
-    <t>#include&lt;iostream&gt;
-#define max 100
-using namespace std;
-void swap(char*&amp;a,char*&amp;b){
-	char t[max];
-	int i=0;
-	while(a[i]!='\0'){
-		t[i]=a[i];i++;}
-	t[i]='\0';
-	i=0;
-	while(b[i]!='0'){
-		a[i]=b[i];i++;}
-	a[i]='\0';
-	i=0;
-	while(t[i]!='\0'){
-		b[i]=t[i];i++;}
-	b[i]='\0';
-	}
-int string_compare(char *a,char*b){
-	int i=0;
-	while(true){
-		if(a[i]=='\0' &amp;&amp; b[i]=='\0') return 0;
-		else if(a[i]=='\0') return -1;
-		else if(b[i]=='\0') return 1;
-		else if(a[i]&gt;b[i]) return 1;
-		else if(a[i]&lt;b[i]) return -1;
-		i++;}
-	}
-int string_sort(char a[][max],int n,int *noc){
-	int count=0;
-	for(int i=0;i&lt;n;i++){
-		bool flag=false;
-		if(i==0) continue;
-		else{
-			int j=i;
-			int gf=string_compare(a[j],a[j-1]);*noc+=1;
-			while(string_compare(a[j],a[j-1])==1){
-				swap(a[j],a[j-1]);count++;
-				j--;flag=true;
-				*noc+=1;
-				if(j==0)break;}}
-		if (flag==false)break;}
-	return count;}
-int main(){
-	int n,noc=0;
-	cin&gt;&gt;n;
-	char words[n][max];
-	for(int i=0;i&lt;n;i++){
-		cin&gt;&gt;words[i];}
-	int h=string_sort(words,n,&amp;noc);
-	for(int i=0;i&lt;n;i++){
-		cout&lt;&lt;words[i]&lt;&lt;'\n';}
-	cout&lt;&lt;noc&lt;&lt;"\n"&lt;&lt;h;}</t>
-  </si>
-  <si>
-    <t>#include&lt;simplecpp&gt;
-main_program{
-	int LCM(int n, int m)
-	{
-	intx;
-	if(m&gt;n)
-		x=n;
-	int gcd;
-	}
-}</t>
   </si>
   <si>
     <t>Write a C++ program to take two inputs from the user, the year N, and d, the day of the week that January 1st falls on. Assume that the days are encoded as follows: (Mon: 1, Tues: 2, Wed: 3,   Sun: 7). Based on this, print all the dates on which Sunday falls on in that year.You must also take into account if the year is a leap year or not. The year is said to be a leap year if the year is divisible by four, except for end-of-century years where the year should be divisible by 400.
@@ -1507,212 +1262,6 @@
   </si>
   <si>
     <t>Poor or No Comments</t>
-  </si>
-  <si>
-    <t>#include&lt;simplecpp&gt;
-bool isleap(int y){
-	if(y%400==0){
-		return true;
-	}
-	else if(y%100!=0&amp;&amp;y%4==0){
-		return true;
-	}
-	else{
-		return false;
-	}
-	}
-main_program{
-int year,pehladin;
-cin&gt;&gt;year&gt;&gt;pehladin;
-int month=1;
-int current_sunday = 8-pehladin;
-cout&lt;&lt;"Month 1:";
-while (true){
-	if (month==1){
-		if(current_sunday&gt;31){
-			month+=1;
-			current_sunday= current_sunday-31;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-cout&lt;&lt;"Month 2:";
-while (true){
-	if (month==2){
-		if(current_sunday&gt;29&amp;&amp;isleap(year)){
-			month+=1;
-			current_sunday= current_sunday-29;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else if(current_sunday&gt;28&amp;&amp;!isleap(year)){
-			month+=1;
-			current_sunday= current_sunday-28;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-cout&lt;&lt;"Month 3:";
-while (true){
-	if (month==3){
-		if(current_sunday&gt;31){
-			month+=1;
-			current_sunday= current_sunday-31;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-cout&lt;&lt;"Month 4:";
-while (true){
-	if (month==4){
-		if(current_sunday&gt;30){
-			month+=1;
-			current_sunday= current_sunday-30;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-cout&lt;&lt;"Month 5:";
-while (true){
-	if (month==5){
-		if(current_sunday&gt;31){
-			month+=1;
-			current_sunday= current_sunday-31;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-cout&lt;&lt;"Month 6:";
-while (true){
-	if (month==6){
-		if(current_sunday&gt;30){
-			month+=1;
-			current_sunday= current_sunday-30;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-cout&lt;&lt;"Month 7:";
-while (true){
-	if (month==7){
-		if(current_sunday&gt;31){
-			month+=1;
-			current_sunday= current_sunday-31;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-cout&lt;&lt;"Month 8:";
-while (true){
-	if (month==8){
-		if(current_sunday&gt;31){
-			month+=1;
-			current_sunday= current_sunday-31;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-cout&lt;&lt;"Month 9:";
-while (true){
-	if (month==9){
-		if(current_sunday&gt;30){
-			month+=1;
-			current_sunday= current_sunday-30;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-cout&lt;&lt;"Month 10:";
-while (true){
-	if (month==10){
-		if(current_sunday&gt;31){
-			month+=1;
-			current_sunday= current_sunday-31;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-cout&lt;&lt;"Month 11:";
-while (true){
-	if (month==11){
-		if(current_sunday&gt;30){
-			month+=1;
-			current_sunday= current_sunday-30;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-cout&lt;&lt;"Month 12:";
-while (true){
-	if (month==12){
-		if(current_sunday&gt;31){
-			month+=1;
-			current_sunday= current_sunday-31;
-			cout&lt;&lt;endl;
-			break;
-			}
-		else{
-			cout&lt;&lt;" "&lt;&lt;current_sunday;
-			current_sunday +=7;
-			}
-		}
-}
-}</t>
   </si>
   <si>
     <t>Write a C++ program to take user input n, the size of a 1D integer array, followed by the array entries as inputs. The program should then determine the majority element of the array, i.e., the element which occurs the most often. It should then display the majority element and how many times it occurs in the array. You may assume that the array contains only non-negative numbers. You may also assume that the array contains only one majority element. 
@@ -1724,41 +1273,6 @@
 Sample output 	3 4	1 4	2 4</t>
   </si>
   <si>
-    <t>#include&lt;iostream&gt;
-using namespace std;
-int main(){
-int n,x;
-int count=0;
-cin&gt;&gt;n;
-int arr[n];
-for(int i=0;i&lt;n;i++){
-cin&gt;&gt;arr[i];}
-if(n==1){cout&lt;&lt;arr[0]&lt;&lt;" "&lt;&lt;n;}
-else{
-for(int i=0;i&lt;n;i++){
-for(int j=i+1;j&lt;n;j++){
-if(arr[i]==arr[j]){count++;
-x=i;}
-else{cout&lt;&lt;"1"&lt;&lt;arr[0];}}
-cout&lt;&lt;arr[x]&lt;&lt;" "&lt;&lt;count;}}
-return 0;}</t>
-  </si>
-  <si>
-    <t>Write a C++ program to accept four numbers from the user a, b, c, and d and compute the addition of (a/b) with (c/d). The formula to compute the addition of two fractions is given below (a*d + b*c)/(c*d). Print the final value as output on the screen.
-Note: Do not write any C++ statements for printing general messages. For example, the following should NOT be present in your program:cout &lt;&lt; "Enter a number:", cout &lt;&lt; "The computed answer is", etc. In addition, do not print unnecessary spaces unless specified in the program. You just have to print the result.</t>
-  </si>
-  <si>
-    <t>#include&lt;simplecpp&gt;
-main_program{
-        float a,b,c,d;
-	cin&gt;&gt;a;
-	cin&gt;&gt;b;
-	cin&gt;&gt;c;
-	cin&gt;&gt;d;
-	if(a&gt;=1 &amp;&amp; b&gt;=1 &amp;&amp; c&gt;=1 &amp;&amp; d&lt;=100){
-		cout&lt;&lt;(a/b)+(c/d);}}</t>
-  </si>
-  <si>
     <t>Write a C++ program to take the dimensions of a matrix (m,n) as input from the user. The program should then take the matrix (let us call it A) itself as input from the user. Following this, the program should compute the product of the transpose of A with A (i.e. ATA of size n x n) and display the result. To accomplish this task, write a function of the form void compute_matrixtranspose_matrix_product (int A[][MAX], int m, int n, int ATA[][MAX]).
 Constraints
 n is a positive integer, m,n &lt;= 8</t>
@@ -1774,119 +1288,6 @@
   </si>
   <si>
     <t>poor or no comments</t>
-  </si>
-  <si>
-    <t>#include&lt;iostream&gt;
-#define max 100
-using namespace std;
-void compute_matrixtranspose_matrix_product (int a[max][max],int m,int n,int ata[max][max]){
-int at[max][max];
-for(int x=0;x&lt;m;x++){
-	for(int y=0;y&lt;n;y++){
-		at[y][x]=a[x][y];
-}
-}
-/*for(int i=0;i&lt;n;i++){
-for(int j=0;j&lt;m;j++){
-cout&lt;&lt;at[i][j]&lt;&lt;" ";}
-cout&lt;&lt;endl;}
-*/
-int i,j,k;
-for(i=0;i&lt;n;i++) {
-for(j=0;j&lt;n;j++){
-			ata[i][j] = 0;
-	for(k=0;k&lt;m;k++){
-			ata[i][j] =ata[i][j]+ at[i][k]*a[k][j];
-			} // 
-} 
-}
-}
-int main(){
-int m,n;
-cin&gt;&gt;m&gt;&gt;n;
-int a[max][max];
-for(int i=0;i&lt;m;i++){
-for(int j=0;j&lt;n;j++){
-cin&gt;&gt;a[i][j];}}
-int ata[max][max];
-compute_matrixtranspose_matrix_product(a, m, n,ata);
-for(int i=0;i&lt;n;i++){
-for(int j=0;j&lt;n;j++){
-cout&lt;&lt;ata[i][j]&lt;&lt;" ";
-}
-cout&lt;&lt;endl;
-}
-return 0;
-}</t>
-  </si>
-  <si>
-    <t>Given a real number y   [0,1], find the value of x, in radians, such that sin(x) = y, without using any trigonometric-inverse function. The value x should lie within the interval [0, pi(3.14) /2]. Write an iterative program that prints the value of x. Do NOT use a brute-force search at all.
-Constraints
-0 &lt;= y &lt;= 1
-0 &lt;= x &lt;=  pi (3.14) /2</t>
-  </si>
-  <si>
-    <t>Implementation of binary search, gradient descent or any appropriate iterative method.</t>
-  </si>
-  <si>
-    <t>Correctly using binary search correct query / Correct iterative update</t>
-  </si>
-  <si>
-    <t>Slight mistake in update of binary search / iterative method</t>
-  </si>
-  <si>
-    <t>Used linear search or completely incorrect search</t>
-  </si>
-  <si>
-    <t>#include&lt;simplecpp&gt;
-main_program{
-	double x;
-	cin &gt;&gt; x;
-        double y=0;
-	while(sin(y)&lt;x &amp;&amp; y&lt;=PI/2){
-		y+=0.0001;
-	}
-	cout &lt;&lt; fixed;
-	cout.precision(3);
-	cout &lt;&lt; y;
-}</t>
-  </si>
-  <si>
-    <t>#include&lt;iostream&gt;
-using namespace std;
-int T(int n,int k){
-    if (n-k &lt;= k){return (0);};
-    return (T(n-1,k-1)+ T(n-2,k) + T(n-3,k));
-}
-int main() {
-    cout &lt;&lt; "";
-    int n,m;
-    cin &gt;&gt; n,m;
-    cout &lt;&lt; T(n,m);
-}</t>
-  </si>
-  <si>
-    <t>#include &lt;simplecpp&gt;
-int string_compare(char *A)
-{
-int c,d;  
-cin&gt;&gt;c&gt;&gt;d;//where c and d refers to the index of the strings or to choose which&gt;
-while (true){
-if (A[c] == 0 &amp;&amp; A[d] == 0) return 0;
-if (A[c] == 0) return -1;
-if (A[d] == 0) return +1; 
-if (A[c] &lt; A[d]) return -1;
-if (A[c] &gt; A[d]) return +1;
-}
-return 0;}
-main_program{
-int n;
-cin&gt;&gt;n;
-char A[12][n];
-for (int i=0;i&lt;11;i++)
-{for (int j=0;j&lt;n;j++)
-{cin&gt;&gt;A[i][j];}}
-int string_compare (char *A);}</t>
   </si>
   <si>
     <t>#include&lt;simplecpp&gt;
@@ -2535,6 +1936,591 @@
      if(sumE&gt;sumO){cout&lt;&lt;sumE&lt;&lt;endl;}
       else{cout&lt;&lt;sumO&lt;&lt;endl;}
 }</t>
+  </si>
+  <si>
+    <t>Function Definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The function is correctly defined (correct return type and arguments with correct dataype). The number of arguments may vary
+</t>
+  </si>
+  <si>
+    <t>#include&lt;iostream&gt;
+using namespace std;
+int main(){
+    int N;
+    cin &gt;&gt; N;
+    int jumps[N];
+    for(int i=0; i&lt;N; i++){
+        cin &gt;&gt; jumps[i];
+    }
+}</t>
+  </si>
+  <si>
+    <t>The problem statement is to find the root of the equation f(x) = x3 - 6x2 + 11x - 6 between x1 and x2 using the bisection method. The input is two high-precision floating-point values of type double representing x1 and x2 respectively. The output is the root of the equation correct up to 3 decimal places. The constraints are that -100 &lt;= x1, x2 &lt;= 100, and x1 &lt; x2. The program should not print any general messages, but only the root of the equation correct up to 3 decimal places.</t>
+  </si>
+  <si>
+    <t>#include&lt;simplecpp&gt;
+main_program{
+	double x1,x2;
+	cin&gt;&gt;x1&gt;&gt;x2;
+	if (x1&gt;=-100 &amp;&amp; x2&lt;=100 &amp;&amp; x2&gt;x1){
+	        if(x1&lt;1 &amp;&amp; x2&gt;1 &amp;&amp; x2&lt;2) cout&lt;&lt;"1.000"&lt;&lt;endl;
+		if(x1&gt;1 &amp;&amp; x1&lt;2 &amp;&amp; x2&gt;2 &amp;&amp; x2&lt;3) cout&lt;&lt;"2.000"&lt;&lt;endl;
+		if(x1&gt;2 &amp;&amp; x1&lt;3 &amp;&amp; x2&gt;3) cout&lt;&lt;"3.000"&lt;&lt;endl;
+		if(x1&lt;1 &amp;&amp; x2&gt;2 &amp;&amp; x2&lt;3) cout&lt;&lt;"1.000"&lt;&lt;"and"&lt;&lt;"2.000"&lt;&lt;endl;
+                if(x1&lt;1 &amp;&amp; x2&gt;3) cout&lt;&lt;"1.000"&lt;&lt;","&lt;&lt;"2.000"&lt;&lt;"and"&lt;&lt;"3.000";
+	}
+}</t>
+  </si>
+  <si>
+    <t>You are given a sequence of integers. Your task is to analyze the order of the elements in the sequence, print the sequence in reverse order, and determine the category of the sequence based on how the elements are arranged.
+Categories
+After reading the sequence, determine which of the following categories it belongs to:
+A - Ascending Order  
+   All elements are in strictly increasing order.
+D - Descending Order  
+   All elements are in strictly decreasing order.
+B - Constant Order  
+   All elements are equal.
+N - None  
+   The sequence does not belong to any of the above categories.
+Your Task
+1. Read an integer n representing the number of elements.
+2. Read n integers into an array or vector.
+3. Print the elements in reverse order.
+4. Traverse the array to determine its category:
+   - If every next element is greater than the previous, it is Ascending (A).
+   - If every next element is smaller than the previous, it is Descending (D).
+   - If all elements are equal, it is Constant (B).
+   - Otherwise, it is None (N).
+5. Print the corresponding category character after printing the reversed array.
+Input Format
+- An integer n.
+- n integers representing the elements of the array.
+Output Format
+- First, print the array in reverse order with spaces.
+- Then print a single character on a new line representing the category:
+  A, D, B, or N.
+Assumptions on Input
+- 1 &lt;= n &lt;= 10^5
+- Elements are integers.</t>
+  </si>
+  <si>
+    <t>Determining Category Constant Values</t>
+  </si>
+  <si>
+    <t>correctly classifies the array as constant</t>
+  </si>
+  <si>
+    <t>Some issue.</t>
+  </si>
+  <si>
+    <t>Major issue.</t>
+  </si>
+  <si>
+    <t>#include&lt;iostream&gt;
+using namespace std;
+int main (){
+    void re(int nums[];int n) {
+for (int i=0; i&lt;n; i++) cin &gt;&gt; A[i];
+}
+    for(int i=0;i&lt;=n/2;i++){
+        int a;
+        nums[i]=a;
+        nums[i]=nums[n-i];
+        nums[n-i]=a; 
+            } 
+            cout&lt;&lt;nums[n];
+}</t>
+  </si>
+  <si>
+    <t>The Taylor series of a function f(x) about a is given by f(x) = f(a) + (x-a) f(1)(a) + [(x-a)2/2! ] f(2)(a) + [(x-a)3/3! ] f(3)(a) + ... + (x-a)n/n! f(n)(a) + ...Here n is the number of terms of the Taylor series expansion and f(n)(a)is the n-th derivative of the function f(x) evaluated at x = a. This formula (with only finitely many terms) is very accurate for x close to a.Write a C++ program that takes a, x, and n as inputs from the user and evaluates the Taylor expansion of f(x) = sin x about a up to n terms. The program should also compute the relative absolute error between the value of the Taylor expansion (let us call it ea) w.r.t. the true value which is sin(a). The formula for this is |ea - sin (a)| / |sin(a)|.The program should print the value of the Taylor expansion as well as the relative absolute error.Â 
+Input Format - a - non zero real number, x,and an integer n
+Output Format - 
+Floating point numbers for the values of the Taylor expansion and the relative error
+Please use before printing the approximated value and the error.
+cout &lt;&lt; fixed;Â  Â  Â  // uses fixed floating point representation
+cout.precision(6);Â  // print six digits after the decimal point
+Constraints
+a not equal to zero
+n is a positive integer
+For higher accuracy, it is advisable for x to be close to a
+Sample input and outputÂ a = pi/3 , x = pi/3 + 0.001, sin(x) is approximately 0.8
+Input           1.047 1.048 100
+Output            0.866426 0.000577
+Note:Do not write any C++ statements for printing general messages. For example, the following should NOT be present in your program:cout &lt;&lt; "Enter a number:",cout &lt;&lt; "The computed answer is", etc.cout should be used to print only the computed final output. In addition, do not print unnecessary spaces unless specified in the questionPlease use cout &lt;&lt; fixed; before printing the approximated value and the error.The solution file name should be an A_Q1.cpp</t>
+  </si>
+  <si>
+    <t>#include&lt;iostream&gt;
+#include&lt;cmath&gt;
+using namespace std;
+int fact (int x){
+int i=1, j=1;
+if ( x==0 || x==1 )
+{
+	return 1;
+}
+else{
+for ( int it=0; it&lt;x; it+=1 )
+{
+	i=j*i;
+	j++;
+}
+return i;
+}
+}
+int main(){
+long double a, x, n, fx, L=1, i=2, j=1;
+cin&gt;&gt;a&gt;&gt;x&gt;&gt;n;
+cout&lt;&lt;fixed;
+cout.precision(6);
+fx= sin(a);
+while(i&lt;n+1)
+{
+	if (int(i)%2==1 &amp;&amp; int(i)%3!=0)
+	{
+		long double k = sin(a), z;
+		for(int it=0; it&lt;i; it+=1 )
+		{
+			j=j*(x-a);
+		}
+		z= (j*k)/ fact(i);
+		fx=fx+z;
+		j==1;
+	}
+		if (int(i)%2==0 &amp;&amp;int(i)%4!=0)
+	{
+		long double k = cos(a), z;
+		for(int it=0; it&lt;i; it+=1 )
+		{
+			j=j*(x-a);
+		}
+		z= (j*k)/ fact(i);
+		fx=fx+z;
+		j=1;
+	}
+		if (int(i)%2==1 &amp;&amp; int(i)%3==0)
+	{
+		long double k = -sin(a), z;
+		for(int it=0; it&lt;i; it+=1 )
+		{
+			j=j*(x-a);
+		}
+		z= (j*k)/ fact(i);
+		fx=fx+z;
+		j=1;
+	}
+		if (int(i)%2==0 &amp;&amp; int(i)%4==0)
+	{
+		long double k = -cos(a), z;
+		for(int it=0; it&lt;i; it+=1 )
+		{
+			j=j*(x-a);
+		}
+		z= (j*k)/ fact(i);
+		fx=fx+z;
+		j=1;
+	}
+	i++;
+}
+L= fabs(fx-sin(a))/fabs(sin(a));
+cout&lt;&lt;fx&lt;&lt;" "&lt;&lt;L;
+}</t>
+  </si>
+  <si>
+    <t>Write a C++ program to take a positive integer n as input from the user and print out its unique prime factors. For this, do the following: While n is divisible by 2, print the number 2 and divide n by 2. After that, the number is no longer even. While n is divisible by k=3, print the number 3 and divide n by 3. After k no longer divides n, increase k by 2 and repeat.Â 
+Input Format - integer n
+Output Format - All prime factors, each one printed on a new line.Â 
+Constraints
+n is a positive integer such that n&gt;=2
+Sample input and output
+Input -Â 45
+Output -Â 3 5
+Explanation:45 can be expressed as 3x3x5 . Hence its prime factors are 3 and 5
+Note:Do not write any C++ statements for printing general messages. For example, the following should NOT be present in your program:cout &lt;&lt; "Enter a number:",cout &lt;&lt; "The computed answer is", etc.cout should be used to print only the computed final output. In addition, do not print unnecessary spaces unless specified in the programThe solution file name should be an C_Q2.cpp</t>
+  </si>
+  <si>
+    <t>#include&lt;iostream&gt;
+using namespace std;
+int main(){
+int n,i,a,p,b;
+cin&gt;&gt;n;
+for(b=2;b&lt;n;b++){
+	if(n%b==0){break;}	
+}
+if(b==n){cout&lt;&lt;n;}
+else{
+for(i=2;i&lt;n;i++){
+	if(i==2){
+		if(n%2==0){cout&lt;&lt;2&lt;&lt;endl;}
+		}
+	else if(i!=2){
+		for(a=2;a&lt;i;a++){if(i%a==0){break;}}
+		if(a==i){p=a;if(n%p==0){cout&lt;&lt;p&lt;&lt;endl;};}
+	}
+	}
+}
+}</t>
+  </si>
+  <si>
+    <t>Write a program to accept two numbers from the user start and end and print the Pythagorean triplets within the range of start to end, both inclusive, but the triplets should not have any common factor. If no such triplets exist, then print 0. The triplets should be in increasing order.</t>
+  </si>
+  <si>
+    <t>#include&lt;simplecpp&gt;
+main_program{
+	int start,end ;
+	cin&gt;&gt; start; cin&gt;&gt; end;
+	int k = 0;
+	int a = 0 ;
+	int b = 0;
+	for(int i = 1 ; i&lt;=(end-start);i++){
+		 a = (start*start) + (start + i)* (start +i);
+		      k =i+ 1;
+ b = (start + k )*(start + k) ;
+if (b == a){
+cout &lt;&lt; start &lt;&lt; ' ' &lt;&lt; start + i &lt;&lt;' ' &lt;&lt;  start + k ;
+}
+k++;
+if ( k == end - start + 1) {
+	break;
+	}
+}
+}</t>
+  </si>
+  <si>
+    <t>Write a C++ program to take the number n and an array A of n numbers as input from the user. The program should then contain a function which determines whether the array is in strictly increasing order (in which case the function should return 1), or else determine whether the array is in strictly decreasing order (in which case the function should return 2), and return 3 otherwise. The format of the function is int isIncreasingDecreasing (int *A, int n). The program should then print the value returned by the function on a new line. You must implement this via a function, otherwise you will get no credit. For simplicity, assume that all entries in the array are unique.
+Input Format - Non-negative integer n and an array A of n elements
+Output Format - The value 1,2 or 3 as described above.Â 
+Constraints
+1 &lt;= n &lt; 25
+Sample input - 33 4 2
+Sample output - 3</t>
+  </si>
+  <si>
+    <t>Quality and number of comments.</t>
+  </si>
+  <si>
+    <t>#include&lt;iostream&gt;
+using namespace std;
+int isIncreasingDecreasing(int *A,int n){
+int j=0,k=0;
+for(int i=0;i&lt;n-1;){
+	if(A[i+1]&gt;A[i]){
+j++;
+i++;
+continue;
+	}
+	else if(A[i+1]&lt;A[i]){
+	k++;i++;
+	continue;
+	}
+	}
+	if(j==n-1){return 1;}
+	else if(k==n-1){return 2;}
+	else{return 3;}
+}
+int main(){
+int n;
+cin&gt;&gt;n;
+int A[n];
+for(int i=0;i&lt;n;i++){
+	cin&gt;&gt;A[i];
+}
+int fun;
+fun=isIncreasingDecreasing(A,n);
+cout&lt;&lt;fun;}</t>
+  </si>
+  <si>
+    <t>Recursion call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correctly sets up the recursive call, with valid parameters and accumulates paths for all valid jumps
+</t>
+  </si>
+  <si>
+    <t>#include&lt;iostream&gt;
+using namespace std;
+int main() {
+    int n;
+    cin&gt;&gt;n;
+   array jumps[n]
+}</t>
+  </si>
+  <si>
+    <t>main: Print Yes or No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correctly prints yes or no according to the function output
+</t>
+  </si>
+  <si>
+    <t>#include&lt;iostream&gt;
+#include&lt;string&gt;
+main_program
+{ 
+    string s1[1000],s2[1000];
+       int sum;
+     cin&gt;&gt;s1;
+    //  cin&gt;&gt;noskipws;
+    getline(cin,s2);
+     int j=0,i=0;
+        while(s1[j]!='\n'){
+      if ( s1[j]==s2[i])
+    {
+    }
+     else
+     {
+        cout&lt;&lt;"no";
+     } j++;
+     while(s2[i]!=" "){
+       i++;
+  } 
+  i++;
+   sum+=1;
+        }
+//     cin&gt;&gt;s1&gt;&gt;s2;
+//     if ( s[0]==s2[0])
+//     {
+//         continue;
+//     }
+//      else
+//      {
+//         cout&lt;&lt;"no";
+//      }
+//   int i=0;
+//   while(s2[i]!=" "){
+//        i++;
+//   }
+//   i++;
+//   if ( s1[1]==s2[i]){
+//     cout&lt;&lt;continue;
+//   }
+//    else{
+//     cout&lt;&lt;"no";
+//    }
+//     while(s2[i]!=" "){
+//        i++;
+//   }i++;
+//   if (s1[2]==s2[i]){
+//     continue;
+//   }
+//   else{
+//     cout&lt;&lt;"no";
+//   }
+}</t>
+  </si>
+  <si>
+    <t>In this problem, you are required to write only two functions in the file implementation.cpp. A main program (main.cpp) is already provided and must not be modified.
+Function 1: noOfDays
+int noOfDays(int m)
+Write a function named noOfDays that takes a single integer m (1 to 12 inclusive) and returns the number of days in that month for the year 2025.
+You may refer to a calendar to determine the correct number of days for each month.
+Examples:
+noOfDays(7) must return 31  
+noOfDays(2) must return 28  
+When this function is called:
+- Argument m is guaranteed to be between 1 and 12.
+--------------------------------------------------
+Function 2: oneWeekLater
+int oneWeekLater(int d, int m)
+Write another function named oneWeekLater which MUST USE the function noOfDays.
+This function takes two integers:
+- d represents the day.
+- m represents the month.
+The function should return a single integer representing the day (between 1 and 31) that occurs exactly 7 days after the given day and month.
+Examples:
+oneWeekLater(20, 8) must return 27  
+oneWeekLater(24, 2) must return 3  
+Explanation:
+- 27 August is 7 days after 20 August.
+- 3 March is 7 days after 24 February.
+When this function is called:
+- Argument d is guaranteed to be between 1 and 31.
+- Argument m is guaranteed to be between 1 and 12.
+--------------------------------------------------
+Main Program
+A main program (main.cpp) is already provided. It reads the day and month from input and calls the functions noOfDays and oneWeekLater with appropriate arguments.
+You must only implement the required functions in implementation.cpp.
+--------------------------------------------------
+Note
+- Do not print any extra messages such as:
+  cout &lt;&lt; "Enter a number"
+  cout &lt;&lt; "The computed answer is"
+- Use cout only to print the computed final output.
+- Do not print unnecessary spaces.
+- Do not hard-code the answers.
+- If any test case passes by simply printing output without logic, marks will not be awarded.</t>
+  </si>
+  <si>
+    <t>Function oneWeekLater: Calling the function noOfDays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correctly calls the function noOfDays from this function to compute the number of days the month has
+</t>
+  </si>
+  <si>
+    <t>#include&lt;simplecpp&gt;
+int noOfDays(int n){
+    if(m==1|)m==5|m==7|m==8|
+    esleif(m==4|m)
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Output
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correctly prints the output
+</t>
+  </si>
+  <si>
+    <t>#include&lt;iostream&gt;
+using namespace std;
+int main(){
+    int n,b=0,c=0;
+    cin&gt;&gt;n;
+    int a[n];
+    for(int i=0; i&lt;n; i++){
+        cin&gt;&gt;a[i];
+    }
+    for(int j=0; j&lt;n; j=j+2){
+        b=b+a[j];
+    }
+     for(int j=1; j&lt;n; j=j+2){
+        c=c+a[j];
+    }
+    cout&lt;&lt;(b&gt;c?b:c);
+}</t>
+  </si>
+  <si>
+    <t>#include&lt;iostream&gt;
+using namespace std;
+void isIncreasingDecreasing(int *A, int n){
+       int c = 0;
+       int h=0;
+          for(int i=1;i&lt;n;i++){
+          int min = A[0];
+          int max = A[n-1];
+               if(min&lt;A[i]){
+               min = A[i];
+               c++;}
+               if(c==n-1){
+               cout&lt;&lt;"1";}
+             else cout&lt;&lt;"3";
+               if(max&lt;A[n-i-i]){
+               max = A[n-i-1];
+               h++;}
+               if(h==n-1){
+               cout&lt;&lt;"2";}
+               else cout&lt;&lt;"3";
+               }
+         }
+int main(){
+int n;
+int A[n];
+cin&gt;&gt;n;
+for(int i=0;i&lt;n;i++){
+cin&gt;&gt;A[i];
+   }
+   isIncreasingDecreasing(A,n);
+   }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prints array/vector in reverse
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correctly prints the array/vector in reverse order
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some issue. </t>
+  </si>
+  <si>
+    <t>#include &lt;iostream&gt;
+using namespace std;
+int main(){
+     int n;
+     cin&gt;&gt;n;
+     int nums[n];
+     for(int i=0; i&lt;n; i++){
+        cin&gt;&gt;nums[i];
+     }
+     int numsr[n];
+     for(int i=0; i&lt;n; i++){
+        numsr[i]= nums[n-i-1];
+     }
+     for(int i=0; i&lt;n; i++){
+        cout&lt;&lt;numsr[i]&lt;&lt;" ";
+     }
+int max = nums[0];
+int min = nums[0];
+int eq = nums[0];
+for(int i=1;i&lt;n+1;i++){
+    if(max&lt;=nums[i]) max=nums[i];}
+    if(max==nums[n-1] &amp;&amp; max!=nums[0]) cout&lt;&lt;"A";
+for(int i=1;i&lt;n+1;i++){
+    if(min&gt;=nums[i]) min=nums[i];}
+    if(min==nums[n-1]&amp;&amp; min!=nums[0]) cout&lt;&lt;"D";
+for(int i=1;i&lt;n+1;i++){
+   if(eq==nums[i]) eq= nums[i];}
+   if(eq==nums[n-1] &amp;&amp; eq==nums[0]) cout&lt;&lt;"B";
+}</t>
+  </si>
+  <si>
+    <t>#include&lt;iostream&gt;
+#define MAX 100
+using namespace std;
+void inp (int A[][MAX], int m, int n)
+{
+ for (int i = 0; i &lt; m; i++)
+ {
+  for (int j = 0; j &lt; n; j++) cin&gt;&gt;A[i][j];
+ }
+}
+void opt (int A[][MAX], int m, int n)
+{
+ for (int i = 0; i &lt; m; i++)
+ {
+  for (int j = 0; j &lt; n; j++) cout&lt;&lt;A[i][j]&lt;&lt;" ";
+  cout&lt;&lt;endl;
+ }
+}
+void compute_matrixtranspose_matrix_product (int A[][MAX], int m, int n, int ATA[][MAX])
+{
+ int AT[MAX][MAX];
+ for (int i = 0; i &lt; m; i++)
+ {
+  for (int j = 0; j &lt; n; j++) AT[j][i] = A[i][j];
+ }
+ for (int i = 0; i &lt; n; i++)
+ {
+  for (int j = 0; j &lt; n; j++)
+  {
+   ATA[i][j] = 0;
+   for (int k = 0; k &lt; m; k++)
+   {
+    ATA[i][j] += AT[i][k]*A[k][j];
+   }
+  }
+ }
+}
+int main()
+{
+ int m, n;
+ cin&gt;&gt;m&gt;&gt;n;
+ int A[MAX][MAX];
+ int ATA[MAX][MAX];
+ inp (A, m, n);
+ compute_matrixtranspose_matrix_product (A, m, n, ATA);
+ opt (ATA, n, n);
+}</t>
+  </si>
+  <si>
+    <t>#include&lt;iostream&gt;
+using namespace std;
+void</t>
   </si>
 </sst>
 </file>
@@ -2590,10 +2576,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3811,439 +3800,439 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>108</v>
+    <row r="32" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="C32">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
-        <v>110</v>
+        <v>3</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="E32" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="F32" t="s">
-        <v>112</v>
-      </c>
-      <c r="G32" t="s">
-        <v>113</v>
-      </c>
-      <c r="H32" t="s">
+        <v>72</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I32" t="s">
         <v>114</v>
       </c>
-      <c r="I32" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>193</v>
       </c>
       <c r="B33" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="E33" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F33" t="s">
-        <v>90</v>
-      </c>
-      <c r="G33" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" t="s">
         <v>117</v>
       </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="I33" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>118</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>196</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
+        <v>197</v>
       </c>
       <c r="E34" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="F34" t="s">
-        <v>122</v>
-      </c>
-      <c r="G34" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" t="s">
-        <v>123</v>
+        <v>199</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="I34" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>124</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="B35" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G35" t="s">
-        <v>13</v>
-      </c>
-      <c r="H35" t="s">
-        <v>127</v>
+        <v>123</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="I35" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>128</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>82</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="E36" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="F36" t="s">
-        <v>72</v>
-      </c>
-      <c r="G36" t="s">
-        <v>13</v>
-      </c>
-      <c r="H36" t="s">
-        <v>131</v>
+        <v>106</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="I36" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>205</v>
+      </c>
+      <c r="B37" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>132</v>
-      </c>
-      <c r="B37" t="s">
-        <v>133</v>
-      </c>
       <c r="C37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="E37" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="F37" t="s">
-        <v>136</v>
-      </c>
-      <c r="G37" t="s">
-        <v>137</v>
-      </c>
-      <c r="H37" t="s">
-        <v>138</v>
+        <v>90</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="I37" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>18</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="E38" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="F38" t="s">
-        <v>126</v>
-      </c>
-      <c r="G38" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" t="s">
-        <v>139</v>
+        <v>123</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="I38" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>140</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
-      <c r="D39" t="s">
-        <v>83</v>
+      <c r="D39" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="E39" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F39" t="s">
-        <v>141</v>
-      </c>
-      <c r="G39" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" t="s">
-        <v>142</v>
+        <v>72</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>212</v>
       </c>
       <c r="I39" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>143</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
-      <c r="D40" t="s">
-        <v>83</v>
+      <c r="D40" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="E40" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="F40" t="s">
-        <v>141</v>
-      </c>
-      <c r="G40" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" t="s">
-        <v>144</v>
+        <v>38</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="I40" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>145</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>216</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>217</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
-      <c r="D41" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" t="s">
-        <v>89</v>
-      </c>
-      <c r="F41" t="s">
-        <v>90</v>
-      </c>
-      <c r="G41" t="s">
-        <v>13</v>
-      </c>
-      <c r="H41" t="s">
-        <v>146</v>
+      <c r="D41" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="I41" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>147</v>
-      </c>
-      <c r="B42" t="s">
-        <v>148</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
-      <c r="D42" t="s">
-        <v>149</v>
+      <c r="D42" s="2" t="s">
+        <v>221</v>
       </c>
       <c r="E42" t="s">
-        <v>150</v>
-      </c>
-      <c r="F42" t="s">
-        <v>151</v>
-      </c>
-      <c r="G42" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42" t="s">
-        <v>152</v>
+        <v>198</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="I42" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>153</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="B43" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="C43">
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="E43" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="F43" t="s">
-        <v>157</v>
-      </c>
-      <c r="G43" t="s">
-        <v>13</v>
-      </c>
-      <c r="H43" t="s">
-        <v>158</v>
+        <v>123</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="I43" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" t="s">
-        <v>35</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>224</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
-      <c r="D44" t="s">
-        <v>36</v>
+      <c r="D44" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>226</v>
       </c>
       <c r="F44" t="s">
-        <v>38</v>
-      </c>
-      <c r="G44" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" t="s">
-        <v>159</v>
+        <v>199</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>41</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="F45" t="s">
-        <v>45</v>
-      </c>
-      <c r="G45" t="s">
-        <v>46</v>
-      </c>
-      <c r="H45" t="s">
-        <v>160</v>
+        <v>129</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="I45" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>20</v>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="B46" t="s">
-        <v>116</v>
+        <v>59</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="E46" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="F46" t="s">
-        <v>90</v>
-      </c>
-      <c r="G46" t="s">
-        <v>13</v>
-      </c>
-      <c r="H46" t="s">
-        <v>21</v>
+        <v>117</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="I46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
@@ -4269,53 +4258,53 @@
         <v>113</v>
       </c>
       <c r="H47" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="I47" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="C48">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="E48" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="F48" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="G48" t="s">
         <v>52</v>
       </c>
       <c r="H48" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="I48" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B49" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
       <c r="D49" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="E49" t="s">
         <v>13</v>
@@ -4324,50 +4313,50 @@
         <v>13</v>
       </c>
       <c r="G49" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="H49" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="I49" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="C50">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="E50" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="F50" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="G50" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="H50" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="I50" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -4376,33 +4365,33 @@
         <v>43</v>
       </c>
       <c r="E51" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="F51" t="s">
         <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="H51" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="I51" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="B52" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="E52" t="s">
         <v>13</v>
@@ -4411,13 +4400,13 @@
         <v>13</v>
       </c>
       <c r="G52" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="H52" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="I52" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
@@ -4443,10 +4432,10 @@
         <v>46</v>
       </c>
       <c r="H53" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="I53" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
@@ -4454,28 +4443,28 @@
         <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="C54">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E54" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="F54" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="G54" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="H54" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="I54" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
@@ -4483,7 +4472,7 @@
         <v>96</v>
       </c>
       <c r="B55" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="C55">
         <v>4</v>
@@ -4495,16 +4484,16 @@
         <v>44</v>
       </c>
       <c r="F55" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="G55" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="H55" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="I55" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
@@ -4512,16 +4501,16 @@
         <v>101</v>
       </c>
       <c r="B56" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="C56">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="E56" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="F56" t="s">
         <v>51</v>
@@ -4530,10 +4519,10 @@
         <v>52</v>
       </c>
       <c r="H56" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="I56" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
@@ -4541,7 +4530,7 @@
         <v>104</v>
       </c>
       <c r="B57" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="C57">
         <v>4</v>
@@ -4553,30 +4542,30 @@
         <v>44</v>
       </c>
       <c r="F57" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="G57" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="H57" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="I57" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="B58" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="C58">
         <v>2</v>
       </c>
       <c r="D58" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="E58" t="s">
         <v>13</v>
@@ -4585,100 +4574,100 @@
         <v>13</v>
       </c>
       <c r="G58" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="H58" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="I58" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="B59" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="C59">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="E59" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="F59" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="G59" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="H59" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="I59" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="B60" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="C60">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="E60" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="F60" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="G60" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="H60" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="I60" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="B61" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="C61">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="E61" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="F61" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="G61" t="s">
         <v>52</v>
       </c>
       <c r="H61" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="I61" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
